--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,709 +808,709 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9397,0.0095,0.0203,0.0033</t>
-  </si>
-  <si>
-    <t>0.0188,0.0001,0.0000,0.9964</t>
-  </si>
-  <si>
-    <t>0.9847,0.0003,0.0009,0.0046</t>
-  </si>
-  <si>
-    <t>0.6003,0.0005,0.0000,0.4183</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9704,0.0026,0.0081,0.0036</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9217,0.0002,0.0016,0.0472</t>
+  </si>
+  <si>
+    <t>0.0852,0.0002,0.0000,0.9684</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7950,0.0003,0.3018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0011,0.9975,0.0002</t>
+  </si>
+  <si>
+    <t>0.0116,0.0005,0.9934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.7984,0.0016,0.2345,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0125,0.9917,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.3124,0.0002,0.5718,0.0067</t>
+  </si>
+  <si>
+    <t>0.0144,0.0002,0.9886,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9966,0.0005</t>
+  </si>
+  <si>
+    <t>0.0051,0.0002,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0040,0.0000,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.1733,0.8435,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9840,0.0073,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.9996,0.0030</t>
+  </si>
+  <si>
+    <t>0.0008,0.9847,0.0911,0.0004</t>
+  </si>
+  <si>
+    <t>0.8501,0.1501,0.0046,0.0013</t>
+  </si>
+  <si>
+    <t>0.9863,0.0029,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.5243,0.6055,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9974,0.0142,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.6569,0.2777,0.0017</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.9933,0.0060</t>
+  </si>
+  <si>
+    <t>0.0028,0.0026,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0043,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9973,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9973,0.0003</t>
+  </si>
+  <si>
+    <t>0.0362,0.1584,0.0045,0.9008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9985,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0078,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0280,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0008,0.9972,0.0002</t>
+  </si>
+  <si>
+    <t>0.9881,0.0100,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9887,0.0066,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.0036,0.9987,0.0031</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9326,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9930,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9434,0.0004,0.0918,0.0001</t>
+  </si>
+  <si>
+    <t>0.4057,0.0006,0.7073,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0024</t>
+  </si>
+  <si>
+    <t>0.0000,0.9932,0.9438,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.9345,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.0482,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.7142,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0000,0.0020,0.9972</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0058,0.0001,0.0103,0.9922</t>
+  </si>
+  <si>
+    <t>0.0051,0.0003,0.0034,0.9953</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9868,0.4419,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9892,0.9765,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.6111,0.9549,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0111,0.9982,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.8998,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9935,0.9652,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9978,0.0026,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.4707,0.0006,0.4528,0.0046</t>
+  </si>
+  <si>
+    <t>0.1093,0.0004,0.9359,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9986,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9978,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0357,0.9682,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.4840,0.0102,0.4430,0.0006</t>
+  </si>
+  <si>
+    <t>0.1625,0.0003,0.8780,0.0003</t>
+  </si>
+  <si>
+    <t>0.8440,0.0286,0.0527,0.0009</t>
+  </si>
+  <si>
+    <t>0.8018,0.0989,0.0091,0.0017</t>
+  </si>
+  <si>
+    <t>0.0014,0.0028,0.1212,0.9521</t>
+  </si>
+  <si>
+    <t>0.0002,0.9986,0.0300,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9651,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9996,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.8942,0.1193,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.1552,0.8730,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0005,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0722,0.9943,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0437,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0028,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9994,0.0004</t>
+  </si>
+  <si>
+    <t>0.9922,0.0001,0.0067,0.0000</t>
+  </si>
+  <si>
+    <t>0.4617,0.0003,0.6767,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.8587,0.0021,0.1533,0.0004</t>
+  </si>
+  <si>
+    <t>0.0635,0.0001,0.0001,0.9812</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0047,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.0004,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.9976,0.0885,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2914,0.7404,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.2806,0.7587,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0226,0.0001,0.0097,0.9800</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9937,0.0335</t>
+  </si>
+  <si>
+    <t>0.9711,0.0002,0.0089,0.0040</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.0210,0.9761,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9887,0.0022,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.7690,0.2145,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.9479,0.0045,0.0322,0.0002</t>
+  </si>
+  <si>
+    <t>0.9827,0.0081,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0014,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9700,0.0289,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8581,0.1832,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9850,0.0213,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.4068,0.0066,0.6589,0.0007</t>
+  </si>
+  <si>
+    <t>0.9879,0.0074,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0019,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0009,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9669,0.0293,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0095,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0452,0.9965,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0023,0.9981,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.0011,0.9945,0.0007</t>
+  </si>
+  <si>
+    <t>0.0078,0.0003,0.9926,0.0003</t>
+  </si>
+  <si>
+    <t>0.0554,0.0050,0.9248,0.0019</t>
+  </si>
+  <si>
+    <t>0.3754,0.0017,0.6175,0.0008</t>
+  </si>
+  <si>
+    <t>0.0823,0.0154,0.8423,0.0006</t>
+  </si>
+  <si>
+    <t>0.2503,0.0053,0.7006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9499,0.0009,0.0475,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.0006,0.9962,0.0005</t>
+  </si>
+  <si>
+    <t>0.0106,0.9890,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0039,0.9949,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.1329,0.9103,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.8604,0.1854,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.0769,0.9367,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.8215,0.1225,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9471,0.0019,0.0182,0.0016</t>
+  </si>
+  <si>
+    <t>0.0357,0.0068,0.9553,0.0005</t>
+  </si>
+  <si>
+    <t>0.1261,0.0037,0.8617,0.0054</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.9982,0.0025</t>
+  </si>
+  <si>
+    <t>0.0008,0.0017,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0073,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.9980,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0116,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0031,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9980,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0052,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0068,0.9932,0.0012</t>
+  </si>
+  <si>
+    <t>0.9281,0.0047,0.0467,0.0052</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0128,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0014,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9987,0.0023</t>
+  </si>
+  <si>
+    <t>0.8948,0.0018,0.0937,0.0003</t>
+  </si>
+  <si>
+    <t>0.0100,0.0001,0.9918,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0001,0.0044,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0014,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9841,0.0002,0.0135,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0003,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0128,0.0082,0.9878,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9819,0.0004,0.0141,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9991,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0112,0.9901,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0597,0.0005,0.9414,0.0012</t>
-  </si>
-  <si>
-    <t>0.1321,0.0002,0.9153,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0747,0.0007,0.9144,0.0014</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0001,0.9949,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.9981,0.0003</t>
-  </si>
-  <si>
-    <t>0.0294,0.9693,0.0014,0.0017</t>
-  </si>
-  <si>
-    <t>0.8677,0.0146,0.0792,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9993,0.0187</t>
-  </si>
-  <si>
-    <t>0.0152,0.5587,0.4379,0.0006</t>
-  </si>
-  <si>
-    <t>0.9924,0.0050,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.8697,0.0641,0.0247,0.0015</t>
-  </si>
-  <si>
-    <t>0.1030,0.9374,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9965,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.0050,0.5360,0.3840,0.0079</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0061,0.0086,0.9838,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0331,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.0176,0.6406,0.0040,0.8133</t>
-  </si>
-  <si>
-    <t>0.0008,0.9959,0.0039,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0003,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0036,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0008,0.9989,0.0113</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0066,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0035,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9945,0.8626,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9679,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9927,0.0003,0.0076,0.0000</t>
-  </si>
-  <si>
-    <t>0.9881,0.0009,0.0080,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.8940,0.9887,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9950,0.9372,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0354,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9843,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.0000,0.0008,0.9976</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0002,0.0028,0.9974</t>
-  </si>
-  <si>
-    <t>0.0017,0.0007,0.0009,0.9984</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0007,0.9880,0.1494,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9851,0.9598,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9512,0.9656,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0314,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.8363,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9897,0.9146,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0191,0.0013,0.9797,0.0009</t>
-  </si>
-  <si>
-    <t>0.9570,0.0007,0.0277,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9987,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.1167,0.9193,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.4602,0.0145,0.3707,0.0036</t>
-  </si>
-  <si>
-    <t>0.0077,0.0016,0.9911,0.0008</t>
-  </si>
-  <si>
-    <t>0.7255,0.0043,0.2758,0.0004</t>
-  </si>
-  <si>
-    <t>0.1893,0.0553,0.3945,0.0153</t>
-  </si>
-  <si>
-    <t>0.0048,0.0026,0.0660,0.9618</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.8716,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.9974,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9604,0.0360,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.6070,0.4731,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9867,0.0001,0.0113,0.0006</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0012,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.3543,0.9903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.4148,0.9916,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0008,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.9321,0.0007,0.0696,0.0003</t>
-  </si>
-  <si>
-    <t>0.1800,0.0009,0.8769,0.0001</t>
-  </si>
-  <si>
-    <t>0.0076,0.0001,0.9930,0.0002</t>
-  </si>
-  <si>
-    <t>0.9089,0.0004,0.1190,0.0001</t>
-  </si>
-  <si>
-    <t>0.0221,0.0001,0.0000,0.9949</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0012,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.3147,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0388,0.9590,0.0011,0.0031</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.7670,0.2335,0.0068,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8588,0.0004,0.0095,0.0930</t>
-  </si>
-  <si>
-    <t>0.0016,0.0019,0.9943,0.0061</t>
-  </si>
-  <si>
-    <t>0.9650,0.0002,0.0109,0.0084</t>
-  </si>
-  <si>
-    <t>0.9963,0.0004,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0070,0.9902,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9848,0.0024,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.9918,0.0016,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.2211,0.5759,0.0305,0.0017</t>
-  </si>
-  <si>
-    <t>0.9691,0.0016,0.0232,0.0002</t>
-  </si>
-  <si>
-    <t>0.8683,0.1098,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0007,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.4532,0.5934,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.5465,0.5297,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.3743,0.5923,0.0133,0.0008</t>
-  </si>
-  <si>
-    <t>0.0010,0.0053,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0021,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2145,0.8334,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.9881,0.0053,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0626,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0034,0.9991,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0011,0.9959,0.0002</t>
-  </si>
-  <si>
-    <t>0.0137,0.0010,0.9862,0.0003</t>
-  </si>
-  <si>
-    <t>0.0021,0.0022,0.9948,0.0005</t>
-  </si>
-  <si>
-    <t>0.0131,0.0006,0.9869,0.0001</t>
-  </si>
-  <si>
-    <t>0.0838,0.0141,0.8652,0.0001</t>
-  </si>
-  <si>
-    <t>0.9517,0.0011,0.0442,0.0000</t>
-  </si>
-  <si>
-    <t>0.9603,0.0003,0.0294,0.0012</t>
-  </si>
-  <si>
-    <t>0.0103,0.0012,0.9890,0.0002</t>
-  </si>
-  <si>
-    <t>0.0076,0.9918,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0111,0.9904,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0225,0.9823,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9753,0.0356,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.2448,0.7871,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9561,0.0210,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0001,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9543,0.0094,0.0061,0.0014</t>
-  </si>
-  <si>
-    <t>0.3293,0.0019,0.7269,0.0003</t>
-  </si>
-  <si>
-    <t>0.3393,0.0003,0.7311,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9994,0.0028</t>
-  </si>
-  <si>
-    <t>0.0011,0.0015,0.9967,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0070,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0058,0.0005,0.9915,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0179,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9922,0.0039,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0822,0.0099,0.8861,0.0006</t>
-  </si>
-  <si>
-    <t>0.9532,0.0009,0.0376,0.0023</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9992,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.1109,0.9981,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.8597,0.0010,0.1204,0.0011</t>
-  </si>
-  <si>
-    <t>0.3475,0.0001,0.7775,0.0002</t>
-  </si>
-  <si>
-    <t>0.9859,0.0002,0.0051,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.0036,0.9916,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0040,0.9980,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0129,0.0002,0.9769,0.0018</t>
-  </si>
-  <si>
-    <t>0.0017,0.0049,0.9942,0.0020</t>
-  </si>
-  <si>
-    <t>0.0121,0.0004,0.9787,0.0028</t>
-  </si>
-  <si>
-    <t>0.9951,0.0001,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.0002,0.0022,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0136,0.0005,0.0011,0.9937</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.4987,0.0002,0.0018,0.5310</t>
+    <t>0.9976,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0057,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0014,0.9989,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.0005,0.9920,0.0003</t>
+  </si>
+  <si>
+    <t>0.1316,0.0029,0.8411,0.0031</t>
+  </si>
+  <si>
+    <t>0.0796,0.0004,0.9208,0.0015</t>
+  </si>
+  <si>
+    <t>0.9862,0.0001,0.0015,0.0054</t>
+  </si>
+  <si>
+    <t>0.0000,0.0070,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0134,0.0006,0.0005,0.9949</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9353,0.0008,0.0021,0.0127</t>
   </si>
 </sst>
 </file>
@@ -1896,7 +1896,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1910,7 +1910,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1924,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,10 +1935,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1952,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1966,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1980,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1994,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2008,7 +2008,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2022,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2036,7 +2036,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2050,7 +2050,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2064,7 +2064,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2078,7 +2078,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2092,7 +2092,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2106,7 +2106,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2120,7 +2120,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2134,7 +2134,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2148,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2162,7 +2162,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2176,7 +2176,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2190,7 +2190,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2204,7 +2204,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2218,7 +2218,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2232,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2246,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2260,7 +2260,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2274,7 +2274,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2288,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2302,7 +2302,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2316,7 +2316,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2330,7 +2330,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2344,7 +2344,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2358,7 +2358,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2372,7 +2372,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2383,10 +2383,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2400,7 +2400,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2414,7 +2414,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2428,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2442,7 +2442,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2456,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2470,7 +2470,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2484,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2498,7 +2498,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2509,10 +2509,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2526,7 +2526,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2540,7 +2540,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2554,7 +2554,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2568,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2582,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2596,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2610,7 +2610,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2708,7 +2708,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2722,7 +2722,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2736,7 +2736,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2750,7 +2750,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2764,7 +2764,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2778,7 +2778,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2792,7 +2792,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2806,7 +2806,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2820,7 +2820,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>280</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2859,7 +2859,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>330</v>
@@ -3184,7 +3184,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3198,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3212,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3226,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3240,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3254,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>355</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3268,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3282,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3296,7 +3296,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3310,7 +3310,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3324,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>358</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3338,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3352,7 +3352,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3363,10 +3363,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3380,7 +3380,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3394,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3408,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3450,7 +3450,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3464,7 +3464,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3478,7 +3478,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3489,10 +3489,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3506,7 +3506,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3520,7 +3520,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3534,7 +3534,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3548,7 +3548,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3562,7 +3562,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3576,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3590,7 +3590,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3604,7 +3604,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3618,7 +3618,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3632,7 +3632,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,10 +3643,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3660,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3716,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3730,7 +3730,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3744,7 +3744,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3758,7 +3758,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3772,7 +3772,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3786,7 +3786,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3800,7 +3800,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3814,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3828,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3842,7 +3842,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3856,7 +3856,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3870,7 +3870,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3884,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3898,7 +3898,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3912,7 +3912,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3926,7 +3926,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3940,7 +3940,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3954,7 +3954,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3968,7 +3968,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3982,7 +3982,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3993,10 +3993,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4010,7 +4010,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4021,10 +4021,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4038,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4052,7 +4052,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4066,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4080,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4094,7 +4094,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4108,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4122,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4133,10 +4133,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4150,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4164,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4178,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>358</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4192,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>414</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4206,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4220,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4234,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4248,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4262,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4276,7 +4276,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4287,10 +4287,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4301,10 +4301,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4315,10 +4315,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4332,7 +4332,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4346,7 +4346,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4360,7 +4360,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4374,7 +4374,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4385,10 +4385,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4402,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4416,7 +4416,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4430,7 +4430,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4444,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4458,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4472,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4486,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4500,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>436</v>
+        <v>287</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4514,7 +4514,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4528,7 +4528,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4542,7 +4542,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4556,7 +4556,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4570,7 +4570,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4584,7 +4584,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4595,10 +4595,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4612,7 +4612,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4626,7 +4626,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4640,7 +4640,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4654,7 +4654,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4668,7 +4668,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4682,7 +4682,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4696,7 +4696,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4710,7 +4710,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4724,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4738,7 +4738,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4752,7 +4752,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4766,7 +4766,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4780,7 +4780,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4794,7 +4794,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4808,7 +4808,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4822,7 +4822,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4836,7 +4836,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4850,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4864,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4878,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4892,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4906,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4920,7 +4920,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>270</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4934,7 +4934,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4948,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>414</v>
+        <v>466</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5046,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5060,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5074,7 +5074,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5088,7 +5088,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5102,7 +5102,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5116,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5130,7 +5130,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5144,7 +5144,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5158,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5172,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>482</v>
+        <v>357</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5186,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5200,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5214,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>355</v>
+        <v>483</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5228,7 +5228,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5242,7 +5242,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5256,7 +5256,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5270,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5284,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5298,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5312,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5326,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>314</v>
+        <v>490</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5424,7 +5424,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>395</v>
+        <v>497</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5449,7 +5449,7 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
         <v>498</v>
